--- a/MSC_IT12523278.xlsx
+++ b/MSC_IT12523278.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc93b88734e820f9/Desktop/cap/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A68C2E71-5C1E-41E0-A0B3-3207E1B20C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{A68C2E71-5C1E-41E0-A0B3-3207E1B20C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FCFEFF2-6633-4D37-8A92-46C13783AB4B}"/>
   <bookViews>
-    <workbookView xWindow="4404" yWindow="396" windowWidth="15624" windowHeight="9324" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,18 @@
   </si>
   <si>
     <t>TIRED</t>
+  </si>
+  <si>
+    <t>exausted</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -398,7 +410,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1077,309 +1101,561 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46241</v>
+      </c>
+      <c r="B8" s="14">
+        <v>400</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>200</v>
+      </c>
+      <c r="E8" s="14">
+        <v>180</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>500</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46242</v>
+      </c>
+      <c r="B9" s="14">
+        <v>500</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>60</v>
+      </c>
+      <c r="E9" s="14">
+        <v>230</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>760</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1580</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
+        <v>-140</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B10" s="14">
+        <v>370</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>70</v>
+      </c>
+      <c r="E10" s="14">
+        <v>120</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>500</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46244</v>
+      </c>
+      <c r="B11" s="14">
+        <v>300</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>90</v>
+      </c>
+      <c r="E11" s="14">
+        <v>100</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>4</v>
+      </c>
+      <c r="H11" s="14">
+        <v>300</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B12" s="14">
+        <v>320</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>78</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>320</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>400</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1178</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
+        <v>262</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B13" s="14">
+        <v>340</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>500</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
+        <v>150</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B14" s="14">
+        <v>400</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>120</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>480</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B15" s="14">
+        <v>540</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>70</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>600</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1540</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
+        <v>-100</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B16" s="14">
+        <v>560</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>80</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>900</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1870</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
+        <v>-430</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B17" s="14">
+        <v>370</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>90</v>
+      </c>
+      <c r="E17" s="14">
+        <v>90</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>730</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1610</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
+        <v>-170</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B18" s="14">
+        <v>340</v>
+      </c>
+      <c r="C18" s="14">
+        <v>40</v>
+      </c>
+      <c r="D18" s="14">
+        <v>70</v>
+      </c>
+      <c r="E18" s="14">
+        <v>90</v>
+      </c>
+      <c r="F18" s="14">
+        <v>150</v>
+      </c>
+      <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="14">
+        <v>450</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>40</v>
+      </c>
+      <c r="D19" s="14">
+        <v>70</v>
+      </c>
+      <c r="E19" s="14">
+        <v>90</v>
+      </c>
+      <c r="F19" s="14">
+        <v>180</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>410</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B20" s="14">
+        <v>500</v>
+      </c>
+      <c r="C20" s="14">
+        <v>40</v>
+      </c>
+      <c r="D20" s="14">
+        <v>80</v>
+      </c>
+      <c r="E20" s="14">
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
+        <v>150</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>120</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B21" s="14">
+        <v>400</v>
+      </c>
+      <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>320</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>130</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
       <c r="N21" s="17"/>
@@ -9754,20 +10030,20 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{C19BAB04-3B31-4B98-97FA-CB27B0DF6775}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{0F3931ED-71D1-4E51-9984-3DFE76BC97C1}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{7C5BE220-557E-41F9-8B64-9258B161129C}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
